--- a/NL217 Computer Programming for Engineering Problems/Excel_Lab/NL217_Excel_Lab_5_HW_XYZ_Class.xlsx
+++ b/NL217 Computer Programming for Engineering Problems/Excel_Lab/NL217_Excel_Lab_5_HW_XYZ_Class.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\A_Subjects\NL217 โปรแกรมคอมพิวเตอร์ในการแก้ปัญหาทางวิศวกรรม\Excel_Lab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DF9A68-C4CC-4412-ADAD-20C3039181AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D2C08-FE60-43CE-B380-5354822F7F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary_Dashboard" sheetId="1" r:id="rId1"/>
@@ -1362,15 +1362,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>189139</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>107496</xdr:rowOff>
+      <xdr:colOff>289992</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>129908</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>15784</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>108028</xdr:rowOff>
+      <xdr:colOff>116637</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>130440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1393,8 +1393,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="189139" y="3384096"/>
-          <a:ext cx="5846445" cy="3810532"/>
+          <a:off x="289992" y="3211526"/>
+          <a:ext cx="5844204" cy="3810532"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
